--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488017_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488017_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.095</v>
+        <v>5.2956</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7452</v>
+        <v>4.423</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3498</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>3.1064</v>
@@ -610,13 +610,13 @@
         <v>1.1893</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7043</v>
+        <v>0.9048</v>
       </c>
       <c r="T2" t="n">
-        <v>0.694</v>
+        <v>0.3718</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0104</v>
+        <v>0.533</v>
       </c>
       <c r="V2" t="n">
         <v>2.0772</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. MORTELLARO</t>
+          <t>H. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.468</v>
+        <v>5.0566</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4461</v>
+        <v>3.6074</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0218</v>
+        <v>1.4492</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8546</v>
+        <v>2.4928</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0492</v>
+        <v>-0.5433</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8054</v>
+        <v>3.0361</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3519</v>
+        <v>2.3163</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2314</v>
+        <v>-0.2952</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1205</v>
+        <v>2.6115</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5027</v>
+        <v>0.1765</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1822</v>
+        <v>-0.2481</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6848</v>
+        <v>0.4246</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3876</v>
+        <v>0.7929</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3876</v>
+        <v>1.784</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7521</v>
+        <v>-0.6434</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6205000000000001</v>
+        <v>-0.132</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1316</v>
+        <v>-0.5113</v>
       </c>
       <c r="V3" t="n">
-        <v>1.4737</v>
+        <v>2.4142</v>
       </c>
       <c r="W3" t="n">
-        <v>1.4737</v>
+        <v>2.4142</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H. VAZQUEZ GARCIA</t>
+          <t>C. MORTELLARO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5586</v>
+        <v>4.8369</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1375</v>
+        <v>3.124</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4211</v>
+        <v>1.713</v>
       </c>
       <c r="G4" t="n">
-        <v>2.4928</v>
+        <v>1.8546</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5433</v>
+        <v>1.0492</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0361</v>
+        <v>0.8054</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3163</v>
+        <v>1.3519</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.2952</v>
+        <v>1.2314</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6115</v>
+        <v>0.1205</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1765</v>
+        <v>0.5027</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2481</v>
+        <v>-0.1822</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4246</v>
+        <v>0.6848</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7929</v>
+        <v>1.3876</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.784</v>
+        <v>1.3876</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1413</v>
+        <v>0.1211</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6019</v>
+        <v>0.2984</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5394</v>
+        <v>-0.1773</v>
       </c>
       <c r="V4" t="n">
-        <v>2.4142</v>
+        <v>1.4737</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4142</v>
+        <v>1.4737</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.196</v>
+        <v>2.4027</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3706</v>
+        <v>0.9423</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8255</v>
+        <v>1.4604</v>
       </c>
       <c r="G5" t="n">
         <v>1.6664</v>
@@ -844,13 +844,13 @@
         <v>1.9822</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.728</v>
+        <v>-0.5213</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7267</v>
+        <v>-0.155</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0013</v>
+        <v>-0.3664</v>
       </c>
       <c r="V5" t="n">
         <v>0.2666</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. DIMITROV KOLEV</t>
+          <t>K. DIKE EGUN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3014</v>
+        <v>1.6308</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9342</v>
+        <v>3.2286</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3672</v>
+        <v>-1.5979</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8421</v>
+        <v>2.7457</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0379</v>
+        <v>2.5984</v>
       </c>
       <c r="I6" t="n">
-        <v>0.88</v>
+        <v>0.1472</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2299</v>
+        <v>1.9774</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0291</v>
+        <v>1.9774</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2009</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3879</v>
+        <v>0.7683</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.067</v>
+        <v>0.621</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6791</v>
+        <v>0.1472</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7929</v>
+        <v>0.5947</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7929</v>
+        <v>0.5947</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0033</v>
+        <v>-0.2359</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3782</v>
+        <v>0.0441</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3748</v>
+        <v>-0.28</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.337</v>
+        <v>-1.4737</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.674</v>
+        <v>1.2071</v>
       </c>
       <c r="X6" t="n">
-        <v>0.337</v>
+        <v>-2.6808</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. DIKE EGUN</t>
+          <t>I. DIMITROV KOLEV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.008</v>
+        <v>1.4127</v>
       </c>
       <c r="E7" t="n">
-        <v>2.634</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.626</v>
+        <v>0.6199</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7457</v>
+        <v>0.8421</v>
       </c>
       <c r="H7" t="n">
-        <v>2.5984</v>
+        <v>-0.0379</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1472</v>
+        <v>0.88</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9774</v>
+        <v>1.2299</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9774</v>
+        <v>1.0291</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.2009</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7683</v>
+        <v>-0.3879</v>
       </c>
       <c r="N7" t="n">
-        <v>0.621</v>
+        <v>-1.067</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1472</v>
+        <v>0.6791</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5947</v>
+        <v>0.7929</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5947</v>
+        <v>0.7929</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8586</v>
+        <v>0.1147</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5505</v>
+        <v>0.2368</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3081</v>
+        <v>-0.1221</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.4737</v>
+        <v>-0.337</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2071</v>
+        <v>-0.674</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.6808</v>
+        <v>0.337</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9608</v>
+        <v>1.3745</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0175</v>
+        <v>0.4874</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9432</v>
+        <v>0.8871</v>
       </c>
       <c r="G8" t="n">
         <v>1.6798</v>
@@ -1078,13 +1078,13 @@
         <v>1.784</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9589</v>
+        <v>-0.5452</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5395</v>
+        <v>-0.0696</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4194</v>
+        <v>-0.4756</v>
       </c>
       <c r="V8" t="n">
         <v>-1.5441</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1668</v>
+        <v>0.1889</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1842</v>
+        <v>0.003</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0174</v>
+        <v>0.1859</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6602</v>
@@ -1312,13 +1312,13 @@
         <v>1.1893</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0418</v>
+        <v>0.3139</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0586</v>
+        <v>0.1286</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0168</v>
+        <v>0.1853</v>
       </c>
       <c r="V11" t="n">
         <v>0.337</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4005</v>
+        <v>0.0269</v>
       </c>
       <c r="E12" t="n">
-        <v>0.039</v>
+        <v>0.1014</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4395</v>
+        <v>-0.0745</v>
       </c>
       <c r="G12" t="n">
         <v>0.3427</v>
@@ -1390,13 +1390,13 @@
         <v>1.784</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4944</v>
+        <v>-0.067</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0772</v>
+        <v>0.1396</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5716</v>
+        <v>-0.2066</v>
       </c>
       <c r="V12" t="n">
         <v>0.9405</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.0045</v>
+        <v>-1.3401</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.2419</v>
+        <v>-1.8301</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2373</v>
+        <v>0.49</v>
       </c>
       <c r="G13" t="n">
         <v>0.6293</v>
@@ -1468,13 +1468,13 @@
         <v>0.5947</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7449</v>
+        <v>0.4093</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9839</v>
+        <v>0.3956</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.239</v>
+        <v>0.0137</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.4302</v>
+        <v>-2.1079</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.9197</v>
+        <v>-0.6536</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.5105</v>
+        <v>-1.4543</v>
       </c>
       <c r="G14" t="n">
         <v>-1.2202</v>
@@ -1546,13 +1546,13 @@
         <v>0.3964</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3993</v>
+        <v>-0.077</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.301</v>
+        <v>-0.0348</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0984</v>
+        <v>-0.0422</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2071</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.9428</v>
+        <v>-4.8866</v>
       </c>
       <c r="E15" t="n">
         <v>-3.5699</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3729</v>
+        <v>-1.3167</v>
       </c>
       <c r="G15" t="n">
         <v>-1.5302</v>
@@ -1624,13 +1624,13 @@
         <v>0.3964</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6196</v>
+        <v>-0.5635</v>
       </c>
       <c r="T15" t="n">
         <v>-0.2496</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.37</v>
+        <v>-0.3139</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2071</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>14.1537</v>
+        <v>15.4017</v>
       </c>
       <c r="E16" t="n">
-        <v>10.9191</v>
+        <v>12.167</v>
       </c>
       <c r="F16" t="n">
-        <v>3.2344</v>
+        <v>3.2346</v>
       </c>
       <c r="G16" t="n">
         <v>13.4599</v>
@@ -1702,13 +1702,13 @@
         <v>13.8755</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.0373</v>
+        <v>-0.7894999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2739999999999999</v>
+        <v>0.9739</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.7632</v>
+        <v>-1.7634</v>
       </c>
       <c r="V16" t="n">
         <v>1.7402</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. CABRERA SALMON</t>
+          <t>J. LOPEZ MUÑOZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8719</v>
+        <v>1.2053</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9672</v>
+        <v>1.2053</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0953</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5911999999999999</v>
+        <v>1.2053</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2909</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8821</v>
+        <v>1.2053</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8548</v>
+        <v>1.2053</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8146</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0402</v>
+        <v>1.2053</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.446</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5237000000000001</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9223</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9911</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.472</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1125</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3596</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. LOPEZ MUÑOZ</t>
+          <t>S. CABRERA SALMON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.2053</v>
+        <v>1.0478</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2053</v>
+        <v>1.1523</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-0.1044</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2053</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.2909</v>
       </c>
       <c r="I18" t="n">
-        <v>1.2053</v>
+        <v>-0.8821</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2053</v>
+        <v>0.8548</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.8146</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2053</v>
+        <v>0.0402</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-1.446</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.5237000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.9223</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>0.6479</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.2975</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.3504</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ</t>
+          <t>A. SEARA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4341</v>
+        <v>0.9913</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9749</v>
+        <v>1.7528</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.7615</v>
       </c>
       <c r="G19" t="n">
-        <v>1.8451</v>
+        <v>-0.4316</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9306</v>
+        <v>-0.5581</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9145</v>
+        <v>0.1265</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0262</v>
+        <v>2.2194</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3834</v>
+        <v>0.633</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6428</v>
+        <v>1.5864</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8189</v>
+        <v>-2.6509</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5472</v>
+        <v>-1.191</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2717</v>
+        <v>-1.4599</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5947</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5947</v>
+        <v>1.5858</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2654</v>
+        <v>0.6122</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0514</v>
+        <v>0.3085</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.214</v>
+        <v>0.3036</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.7403</v>
+        <v>1.2071</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7403</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SEARA RODRIGUEZ</t>
+          <t>M. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1717</v>
+        <v>0.8344</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3453</v>
+        <v>1.1786</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1735</v>
+        <v>-0.3442</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.4316</v>
+        <v>1.8451</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5581</v>
+        <v>0.9306</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1265</v>
+        <v>0.9145</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2194</v>
+        <v>1.0262</v>
       </c>
       <c r="K20" t="n">
-        <v>0.633</v>
+        <v>0.3834</v>
       </c>
       <c r="L20" t="n">
-        <v>1.5864</v>
+        <v>0.6428</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.6509</v>
+        <v>0.8189</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.191</v>
+        <v>0.5472</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4599</v>
+        <v>0.2717</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3964</v>
+        <v>0.5947</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5858</v>
+        <v>0.5947</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2074</v>
+        <v>0.1349</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0989</v>
+        <v>0.1524</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1084</v>
+        <v>-0.0175</v>
       </c>
       <c r="V20" t="n">
-        <v>1.2071</v>
+        <v>-1.7403</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.7403</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. STACHOVSKIJ</t>
+          <t>P. PERALES FERNANDEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3003</v>
+        <v>-0.1521</v>
       </c>
       <c r="E21" t="n">
-        <v>2.1768</v>
+        <v>-0.6684</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4771</v>
+        <v>0.5163</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7133</v>
+        <v>-1.127</v>
       </c>
       <c r="H21" t="n">
-        <v>1.7127</v>
+        <v>-0.3981</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.426</v>
+        <v>-0.7289</v>
       </c>
       <c r="J21" t="n">
-        <v>2.415</v>
+        <v>-0.9349</v>
       </c>
       <c r="K21" t="n">
-        <v>2.9736</v>
+        <v>-0.3361</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.5586</v>
+        <v>-0.5988</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.1283</v>
+        <v>-0.1922</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2609</v>
+        <v>-0.062</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.8674</v>
+        <v>-0.1301</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.5858</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9733</v>
+        <v>-0.9911</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3876</v>
+        <v>0.3964</v>
       </c>
       <c r="S21" t="n">
-        <v>2.6023</v>
+        <v>0.3625</v>
       </c>
       <c r="T21" t="n">
-        <v>1.865</v>
+        <v>0.0505</v>
       </c>
       <c r="U21" t="n">
-        <v>0.7373</v>
+        <v>0.312</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6036</v>
+        <v>1.2071</v>
       </c>
       <c r="W21" t="n">
-        <v>0.8701</v>
+        <v>1.2071</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. PERALES FERNANDEZ</t>
+          <t>T. YOME</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3898</v>
+        <v>-0.2369</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7703</v>
+        <v>-0.707</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3805</v>
+        <v>0.4701</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.127</v>
+        <v>0.055</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3981</v>
+        <v>1.6639</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7289</v>
+        <v>-1.6089</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9349</v>
+        <v>0.2938</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.3361</v>
+        <v>1.6482</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5988</v>
+        <v>-1.3544</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1922</v>
+        <v>-0.2388</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.062</v>
+        <v>0.0157</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1301</v>
+        <v>-0.2545</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.5947</v>
+        <v>0.9911</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3964</v>
+        <v>1.9822</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1248</v>
+        <v>-0.0055</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0514</v>
+        <v>0.0607</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1762</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>1.2071</v>
+        <v>-1.2775</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2071</v>
+        <v>-0.0704</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. GARCIA TEJON</t>
+          <t>L. FURLAN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9403</v>
+        <v>-0.2913</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5758</v>
+        <v>2.0343</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3645</v>
+        <v>-2.3256</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.0879</v>
+        <v>-0.1354</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5153</v>
+        <v>1.2441</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.5726</v>
+        <v>-1.3795</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.4908</v>
+        <v>2.3875</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1482</v>
+        <v>2.3072</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.639</v>
+        <v>0.0804</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.5971</v>
+        <v>-2.5229</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6634</v>
+        <v>-1.0631</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9337</v>
+        <v>-1.4599</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1982</v>
+        <v>1.3876</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1893</v>
+        <v>1.3876</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2577</v>
+        <v>-0.0697</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.301</v>
+        <v>-0.3532</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0432</v>
+        <v>0.2835</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2071</v>
+        <v>-1.4737</v>
       </c>
       <c r="W23" t="n">
-        <v>1.2071</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. CASIN LORENTE</t>
+          <t>A. GARCIA TEJON</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.0607</v>
+        <v>-0.589</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.659</v>
+        <v>-0.1683</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4018</v>
+        <v>-0.4207</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.0607</v>
+        <v>-2.0879</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.659</v>
+        <v>-0.5153</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.4018</v>
+        <v>-1.5726</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.659</v>
+        <v>-0.4908</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.659</v>
+        <v>0.1482</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-0.639</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4018</v>
+        <v>-1.5971</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>-0.6634</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4018</v>
+        <v>-0.9337</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>0.1982</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>0.0936</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>0.1065</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>-0.0129</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.2071</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>L. FURLAN</t>
+          <t>J. CASIN LORENTE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.1565</v>
+        <v>-1.0607</v>
       </c>
       <c r="E25" t="n">
-        <v>1.525</v>
+        <v>-0.659</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.6815</v>
+        <v>-0.4018</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1354</v>
+        <v>-1.0607</v>
       </c>
       <c r="H25" t="n">
-        <v>1.2441</v>
+        <v>-0.659</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.3795</v>
+        <v>-0.4018</v>
       </c>
       <c r="J25" t="n">
-        <v>2.3875</v>
+        <v>-0.659</v>
       </c>
       <c r="K25" t="n">
-        <v>2.3072</v>
+        <v>-0.659</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0804</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.5229</v>
+        <v>-0.4018</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.0631</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.4599</v>
+        <v>-0.4018</v>
       </c>
       <c r="P25" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9350000000000001</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8625</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.07240000000000001</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>T. YOME</t>
+          <t>D. STACHOVSKIJ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.1851</v>
+        <v>-1.7637</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.3182</v>
+        <v>0.7506</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1331</v>
+        <v>-2.5143</v>
       </c>
       <c r="G26" t="n">
-        <v>0.055</v>
+        <v>-0.7133</v>
       </c>
       <c r="H26" t="n">
-        <v>1.6639</v>
+        <v>1.7127</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.6089</v>
+        <v>-2.426</v>
       </c>
       <c r="J26" t="n">
-        <v>0.2938</v>
+        <v>2.415</v>
       </c>
       <c r="K26" t="n">
-        <v>1.6482</v>
+        <v>2.9736</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.3544</v>
+        <v>-0.5586</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2388</v>
+        <v>-3.1283</v>
       </c>
       <c r="N26" t="n">
-        <v>0.0157</v>
+        <v>-1.2609</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.2545</v>
+        <v>-1.8674</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9911</v>
+        <v>-1.5858</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.9911</v>
+        <v>-2.9733</v>
       </c>
       <c r="R26" t="n">
-        <v>1.9822</v>
+        <v>1.3876</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.9537</v>
+        <v>1.1389</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.5505</v>
+        <v>0.4388</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4031</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.2775</v>
+        <v>-0.6036</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.0704</v>
+        <v>0.8701</v>
       </c>
       <c r="X26" t="n">
-        <v>-1.2071</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-2.9238</v>
+        <v>-2.8546</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.3855</v>
+        <v>-1.2836</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.5383</v>
+        <v>-1.571</v>
       </c>
       <c r="G27" t="n">
         <v>0.2364</v>
@@ -2560,13 +2560,13 @@
         <v>1.1893</v>
       </c>
       <c r="S27" t="n">
-        <v>0.3134</v>
+        <v>0.3827</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2534</v>
+        <v>0.3553</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0601</v>
+        <v>0.0274</v>
       </c>
       <c r="V27" t="n">
         <v>-2.6808</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-3.2867</v>
+        <v>-3.5525</v>
       </c>
       <c r="E28" t="n">
-        <v>-3.2714</v>
+        <v>-3.7807</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0153</v>
+        <v>0.2282</v>
       </c>
       <c r="G28" t="n">
         <v>-4.4186</v>
@@ -2638,13 +2638,13 @@
         <v>0.9911</v>
       </c>
       <c r="S28" t="n">
-        <v>0.6494</v>
+        <v>0.3836</v>
       </c>
       <c r="T28" t="n">
-        <v>0.8077</v>
+        <v>0.2984</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.1583</v>
+        <v>0.0852</v>
       </c>
       <c r="V28" t="n">
         <v>1.4737</v>
@@ -2671,13 +2671,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>-6.5936</v>
+        <v>-5.6944</v>
       </c>
       <c r="E29" t="n">
-        <v>-4.4491</v>
+        <v>-4.0416</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.1445</v>
+        <v>-1.6528</v>
       </c>
       <c r="G29" t="n">
         <v>-6.2358</v>
@@ -2716,13 +2716,13 @@
         <v>1.1893</v>
       </c>
       <c r="S29" t="n">
-        <v>-0.5054</v>
+        <v>0.3938</v>
       </c>
       <c r="T29" t="n">
-        <v>-0.3596</v>
+        <v>0.0479</v>
       </c>
       <c r="U29" t="n">
-        <v>-0.1459</v>
+        <v>0.3459</v>
       </c>
       <c r="V29" t="n">
         <v>0.9405</v>
@@ -2749,13 +2749,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>-14.1538</v>
+        <v>-12.1164</v>
       </c>
       <c r="E30" t="n">
-        <v>-3.234799999999998</v>
+        <v>-3.234699999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>-10.919</v>
+        <v>-8.8817</v>
       </c>
       <c r="G30" t="n">
         <v>-13.4597</v>
@@ -2770,7 +2770,7 @@
         <v>2.7163</v>
       </c>
       <c r="K30" t="n">
-        <v>5.546999999999999</v>
+        <v>5.547000000000001</v>
       </c>
       <c r="L30" t="n">
         <v>-2.830699999999999</v>
@@ -2785,7 +2785,7 @@
         <v>-9.930399999999999</v>
       </c>
       <c r="P30" t="n">
-        <v>-0.9911000000000006</v>
+        <v>-0.9911000000000004</v>
       </c>
       <c r="Q30" t="n">
         <v>-13.8754</v>
@@ -2794,13 +2794,13 @@
         <v>12.8844</v>
       </c>
       <c r="S30" t="n">
-        <v>2.037300000000001</v>
+        <v>4.0749</v>
       </c>
       <c r="T30" t="n">
         <v>1.7633</v>
       </c>
       <c r="U30" t="n">
-        <v>0.2743</v>
+        <v>2.3115</v>
       </c>
       <c r="V30" t="n">
         <v>-1.7404</v>
